--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>126826809</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126826888</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126826728</v>
+        <v>126825913</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436887</v>
+        <v>436759</v>
       </c>
       <c r="R5" t="n">
-        <v>6759925</v>
+        <v>6759891</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På flera tallstammar</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126825913</v>
+        <v>126826728</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436759</v>
+        <v>436887</v>
       </c>
       <c r="R6" t="n">
-        <v>6759891</v>
+        <v>6759925</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>På flera tallstammar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1228,7 @@
         <v>126826931</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>126826915</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,32 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126826327</v>
+        <v>126826644</v>
       </c>
       <c r="B9" t="n">
-        <v>75014</v>
+        <v>91339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436654</v>
+        <v>436837</v>
       </c>
       <c r="R9" t="n">
-        <v>6759868</v>
+        <v>6759907</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1546,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126826644</v>
+        <v>126826327</v>
       </c>
       <c r="B10" t="n">
-        <v>91265</v>
+        <v>75073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436837</v>
+        <v>436654</v>
       </c>
       <c r="R10" t="n">
-        <v>6759907</v>
+        <v>6759868</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,41 +1653,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126828249</v>
+        <v>126826289</v>
       </c>
       <c r="B11" t="n">
-        <v>98281</v>
+        <v>57817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223597</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Atugaturis, Atugaturis, Dlr</t>
+          <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436465</v>
+        <v>436658</v>
       </c>
       <c r="R11" t="n">
-        <v>6759903</v>
+        <v>6759873</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1719,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1729,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,54 +1769,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126826289</v>
+        <v>126828249</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>98356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>223597</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råmossmyren, Råmossmyren, Dlr</t>
+          <t>Atugaturis, Atugaturis, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436658</v>
+        <v>436465</v>
       </c>
       <c r="R12" t="n">
-        <v>6759873</v>
+        <v>6759903</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,7 +1875,7 @@
         <v>126824791</v>
       </c>
       <c r="B13" t="n">
-        <v>75014</v>
+        <v>75073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>126825928</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>126825890</v>
       </c>
       <c r="B15" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>126827015</v>
       </c>
       <c r="B16" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>126826957</v>
       </c>
       <c r="B17" t="n">
-        <v>79004</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>126825163</v>
       </c>
       <c r="B20" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>126827600</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2864,6 +2864,366 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127284718</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>venjan, Venjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>436590</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6759954</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127284637</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>venjan, Venjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>436603</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6759843</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127284698</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>venjan, Venjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>436602</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6759946</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126826809</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126826888</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126825913</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>126826728</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>126826931</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>126826915</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>126826644</v>
       </c>
       <c r="B9" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>126826327</v>
       </c>
       <c r="B10" t="n">
-        <v>75073</v>
+        <v>75076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>126828249</v>
       </c>
       <c r="B12" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>126824791</v>
       </c>
       <c r="B13" t="n">
-        <v>75073</v>
+        <v>75076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>126825928</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>126825890</v>
       </c>
       <c r="B15" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>126827015</v>
       </c>
       <c r="B16" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>126826957</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2644,45 +2644,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126825163</v>
+        <v>126827600</v>
       </c>
       <c r="B20" t="n">
-        <v>75135</v>
+        <v>98442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436643</v>
+        <v>436644</v>
       </c>
       <c r="R20" t="n">
-        <v>6759772</v>
+        <v>6759919</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2714,7 +2723,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2724,7 +2733,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2751,54 +2760,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126827600</v>
+        <v>126825163</v>
       </c>
       <c r="B21" t="n">
-        <v>98436</v>
+        <v>75138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436644</v>
+        <v>436643</v>
       </c>
       <c r="R21" t="n">
-        <v>6759919</v>
+        <v>6759772</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2870,7 +2870,7 @@
         <v>127284718</v>
       </c>
       <c r="B22" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>127284637</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>127284698</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -889,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126826570</v>
+        <v>126825913</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436813</v>
+        <v>436759</v>
       </c>
       <c r="R4" t="n">
-        <v>6759931</v>
+        <v>6759891</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126825913</v>
+        <v>126826728</v>
       </c>
       <c r="B5" t="n">
         <v>79014</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436759</v>
+        <v>436887</v>
       </c>
       <c r="R5" t="n">
-        <v>6759891</v>
+        <v>6759925</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>På flera tallstammar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,45 +1113,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126826728</v>
+        <v>126826570</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436887</v>
+        <v>436813</v>
       </c>
       <c r="R6" t="n">
-        <v>6759925</v>
+        <v>6759931</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1183,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,12 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera tallstammar</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2644,54 +2644,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126827600</v>
+        <v>126825163</v>
       </c>
       <c r="B20" t="n">
-        <v>98442</v>
+        <v>75138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436644</v>
+        <v>436643</v>
       </c>
       <c r="R20" t="n">
-        <v>6759919</v>
+        <v>6759772</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2723,7 +2714,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2733,7 +2724,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,45 +2751,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126825163</v>
+        <v>126827600</v>
       </c>
       <c r="B21" t="n">
-        <v>75138</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436643</v>
+        <v>436644</v>
       </c>
       <c r="R21" t="n">
-        <v>6759772</v>
+        <v>6759919</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -889,45 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126825913</v>
+        <v>126826570</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436759</v>
+        <v>436813</v>
       </c>
       <c r="R4" t="n">
-        <v>6759891</v>
+        <v>6759931</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126826728</v>
+        <v>126825913</v>
       </c>
       <c r="B5" t="n">
         <v>79014</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436887</v>
+        <v>436759</v>
       </c>
       <c r="R5" t="n">
-        <v>6759925</v>
+        <v>6759891</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På flera tallstammar</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,50 +1113,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126826570</v>
+        <v>126826728</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436813</v>
+        <v>436887</v>
       </c>
       <c r="R6" t="n">
-        <v>6759931</v>
+        <v>6759925</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1193,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På flera tallstammar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1653,54 +1653,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126826289</v>
+        <v>126828249</v>
       </c>
       <c r="B11" t="n">
-        <v>57817</v>
+        <v>98362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>223597</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Råmossmyren, Råmossmyren, Dlr</t>
+          <t>Atugaturis, Atugaturis, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436658</v>
+        <v>436465</v>
       </c>
       <c r="R11" t="n">
-        <v>6759873</v>
+        <v>6759903</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1732,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,41 +1756,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126828249</v>
+        <v>126826289</v>
       </c>
       <c r="B12" t="n">
-        <v>98362</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223597</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Atugaturis, Atugaturis, Dlr</t>
+          <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436465</v>
+        <v>436658</v>
       </c>
       <c r="R12" t="n">
-        <v>6759903</v>
+        <v>6759873</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -889,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126826570</v>
+        <v>126826728</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436813</v>
+        <v>436887</v>
       </c>
       <c r="R4" t="n">
-        <v>6759931</v>
+        <v>6759925</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera tallstammar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1113,45 +1113,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126826728</v>
+        <v>126826570</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436887</v>
+        <v>436813</v>
       </c>
       <c r="R6" t="n">
-        <v>6759925</v>
+        <v>6759931</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1183,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,12 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera tallstammar</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1439,32 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126826644</v>
+        <v>126826327</v>
       </c>
       <c r="B9" t="n">
-        <v>91345</v>
+        <v>75076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436837</v>
+        <v>436654</v>
       </c>
       <c r="R9" t="n">
-        <v>6759907</v>
+        <v>6759868</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1546,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126826327</v>
+        <v>126826644</v>
       </c>
       <c r="B10" t="n">
-        <v>75076</v>
+        <v>91346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436654</v>
+        <v>436837</v>
       </c>
       <c r="R10" t="n">
-        <v>6759868</v>
+        <v>6759907</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,41 +1653,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126828249</v>
+        <v>126826289</v>
       </c>
       <c r="B11" t="n">
-        <v>98362</v>
+        <v>57817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223597</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Atugaturis, Atugaturis, Dlr</t>
+          <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436465</v>
+        <v>436658</v>
       </c>
       <c r="R11" t="n">
-        <v>6759903</v>
+        <v>6759873</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1719,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1729,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,54 +1769,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126826289</v>
+        <v>126828249</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>98363</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>223597</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råmossmyren, Råmossmyren, Dlr</t>
+          <t>Atugaturis, Atugaturis, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436658</v>
+        <v>436465</v>
       </c>
       <c r="R12" t="n">
-        <v>6759873</v>
+        <v>6759903</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2094,7 +2094,7 @@
         <v>126825890</v>
       </c>
       <c r="B15" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>126827015</v>
       </c>
       <c r="B16" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>126827600</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>127284718</v>
       </c>
       <c r="B22" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>127284637</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>127284698</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126826728</v>
+        <v>126825913</v>
       </c>
       <c r="B4" t="n">
         <v>79014</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436887</v>
+        <v>436759</v>
       </c>
       <c r="R4" t="n">
-        <v>6759925</v>
+        <v>6759891</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera tallstammar</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126825913</v>
+        <v>126826728</v>
       </c>
       <c r="B5" t="n">
         <v>79014</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436759</v>
+        <v>436887</v>
       </c>
       <c r="R5" t="n">
-        <v>6759891</v>
+        <v>6759925</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>På flera tallstammar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1653,54 +1653,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126826289</v>
+        <v>126828249</v>
       </c>
       <c r="B11" t="n">
-        <v>57817</v>
+        <v>98363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>223597</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Råmossmyren, Råmossmyren, Dlr</t>
+          <t>Atugaturis, Atugaturis, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436658</v>
+        <v>436465</v>
       </c>
       <c r="R11" t="n">
-        <v>6759873</v>
+        <v>6759903</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1732,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,41 +1756,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126828249</v>
+        <v>126826289</v>
       </c>
       <c r="B12" t="n">
-        <v>98363</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223597</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Atugaturis, Atugaturis, Dlr</t>
+          <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436465</v>
+        <v>436658</v>
       </c>
       <c r="R12" t="n">
-        <v>6759903</v>
+        <v>6759873</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -1439,32 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126826327</v>
+        <v>126826644</v>
       </c>
       <c r="B9" t="n">
-        <v>75076</v>
+        <v>91346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436654</v>
+        <v>436837</v>
       </c>
       <c r="R9" t="n">
-        <v>6759868</v>
+        <v>6759907</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1546,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126826644</v>
+        <v>126826327</v>
       </c>
       <c r="B10" t="n">
-        <v>91346</v>
+        <v>75076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436837</v>
+        <v>436654</v>
       </c>
       <c r="R10" t="n">
-        <v>6759907</v>
+        <v>6759868</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2091,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126825890</v>
+        <v>126827015</v>
       </c>
       <c r="B15" t="n">
         <v>91346</v>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436770</v>
+        <v>436942</v>
       </c>
       <c r="R15" t="n">
-        <v>6759889</v>
+        <v>6760013</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,7 +2198,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126827015</v>
+        <v>126825890</v>
       </c>
       <c r="B16" t="n">
         <v>91346</v>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436942</v>
+        <v>436770</v>
       </c>
       <c r="R16" t="n">
-        <v>6760013</v>
+        <v>6759889</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2644,45 +2644,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126825163</v>
+        <v>126827600</v>
       </c>
       <c r="B20" t="n">
-        <v>75138</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436643</v>
+        <v>436644</v>
       </c>
       <c r="R20" t="n">
-        <v>6759772</v>
+        <v>6759919</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2714,7 +2723,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2724,7 +2733,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2751,54 +2760,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126827600</v>
+        <v>126825163</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>75138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436644</v>
+        <v>436643</v>
       </c>
       <c r="R21" t="n">
-        <v>6759919</v>
+        <v>6759772</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -2091,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126827015</v>
+        <v>126825890</v>
       </c>
       <c r="B15" t="n">
         <v>91346</v>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436942</v>
+        <v>436770</v>
       </c>
       <c r="R15" t="n">
-        <v>6760013</v>
+        <v>6759889</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,7 +2198,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126825890</v>
+        <v>126827015</v>
       </c>
       <c r="B16" t="n">
         <v>91346</v>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436770</v>
+        <v>436942</v>
       </c>
       <c r="R16" t="n">
-        <v>6759889</v>
+        <v>6760013</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126826809</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126826888</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126825913</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126826728</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>126826570</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>126826931</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>126826915</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>126826644</v>
       </c>
       <c r="B9" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>126826327</v>
       </c>
       <c r="B10" t="n">
-        <v>75076</v>
+        <v>75080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,41 +1653,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126828249</v>
+        <v>126826289</v>
       </c>
       <c r="B11" t="n">
-        <v>98363</v>
+        <v>57821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223597</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Atugaturis, Atugaturis, Dlr</t>
+          <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436465</v>
+        <v>436658</v>
       </c>
       <c r="R11" t="n">
-        <v>6759903</v>
+        <v>6759873</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1719,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1729,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,54 +1769,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126826289</v>
+        <v>126828249</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>98367</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>223597</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råmossmyren, Råmossmyren, Dlr</t>
+          <t>Atugaturis, Atugaturis, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436658</v>
+        <v>436465</v>
       </c>
       <c r="R12" t="n">
-        <v>6759873</v>
+        <v>6759903</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,7 +1875,7 @@
         <v>126824791</v>
       </c>
       <c r="B13" t="n">
-        <v>75076</v>
+        <v>75080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>126825928</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>126825890</v>
       </c>
       <c r="B15" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>126827015</v>
       </c>
       <c r="B16" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>126826957</v>
       </c>
       <c r="B17" t="n">
-        <v>79038</v>
+        <v>79042</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>126828191</v>
       </c>
       <c r="B18" t="n">
-        <v>4772</v>
+        <v>4773</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>126825242</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,54 +2644,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126827600</v>
+        <v>126825163</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>75142</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436644</v>
+        <v>436643</v>
       </c>
       <c r="R20" t="n">
-        <v>6759919</v>
+        <v>6759772</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2723,7 +2714,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2733,7 +2724,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,45 +2751,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126825163</v>
+        <v>126827600</v>
       </c>
       <c r="B21" t="n">
-        <v>75138</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436643</v>
+        <v>436644</v>
       </c>
       <c r="R21" t="n">
-        <v>6759772</v>
+        <v>6759919</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2870,7 +2870,7 @@
         <v>127284718</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>127284637</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>127284698</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -1439,32 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126826644</v>
+        <v>126826327</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>75080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436837</v>
+        <v>436654</v>
       </c>
       <c r="R9" t="n">
-        <v>6759907</v>
+        <v>6759868</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1546,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126826327</v>
+        <v>126826644</v>
       </c>
       <c r="B10" t="n">
-        <v>75080</v>
+        <v>91350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436654</v>
+        <v>436837</v>
       </c>
       <c r="R10" t="n">
-        <v>6759868</v>
+        <v>6759907</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -2644,45 +2644,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126825163</v>
+        <v>126827600</v>
       </c>
       <c r="B20" t="n">
-        <v>75142</v>
+        <v>98447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436643</v>
+        <v>436644</v>
       </c>
       <c r="R20" t="n">
-        <v>6759772</v>
+        <v>6759919</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2714,7 +2723,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2724,7 +2733,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2751,54 +2760,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126827600</v>
+        <v>126825163</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>75142</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436644</v>
+        <v>436643</v>
       </c>
       <c r="R21" t="n">
-        <v>6759919</v>
+        <v>6759772</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -1439,32 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126826327</v>
+        <v>126826644</v>
       </c>
       <c r="B9" t="n">
-        <v>75080</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436654</v>
+        <v>436837</v>
       </c>
       <c r="R9" t="n">
-        <v>6759868</v>
+        <v>6759907</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1546,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126826644</v>
+        <v>126826327</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>75080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436837</v>
+        <v>436654</v>
       </c>
       <c r="R10" t="n">
-        <v>6759907</v>
+        <v>6759868</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,7 +1772,7 @@
         <v>126828249</v>
       </c>
       <c r="B12" t="n">
-        <v>98367</v>
+        <v>98368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2644,54 +2644,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126827600</v>
+        <v>126825163</v>
       </c>
       <c r="B20" t="n">
-        <v>98447</v>
+        <v>75142</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436644</v>
+        <v>436643</v>
       </c>
       <c r="R20" t="n">
-        <v>6759919</v>
+        <v>6759772</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2723,7 +2714,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2733,7 +2724,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,45 +2751,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126825163</v>
+        <v>126827600</v>
       </c>
       <c r="B21" t="n">
-        <v>75142</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436643</v>
+        <v>436644</v>
       </c>
       <c r="R21" t="n">
-        <v>6759772</v>
+        <v>6759919</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2870,7 +2870,7 @@
         <v>127284718</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>127284637</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>127284698</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -2870,7 +2870,7 @@
         <v>127284718</v>
       </c>
       <c r="B22" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>127284637</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>127284698</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -2870,7 +2870,7 @@
         <v>127284718</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>127284637</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>127284698</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -2870,7 +2870,7 @@
         <v>127284718</v>
       </c>
       <c r="B22" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>127284637</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>127284698</v>
       </c>
       <c r="B24" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -2870,7 +2870,7 @@
         <v>127284718</v>
       </c>
       <c r="B22" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>127284637</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>127284698</v>
       </c>
       <c r="B24" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -2870,7 +2870,7 @@
         <v>127284718</v>
       </c>
       <c r="B22" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>127284637</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>127284698</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126826809</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126826888</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,45 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126825913</v>
+        <v>126826570</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436759</v>
+        <v>436813</v>
       </c>
       <c r="R4" t="n">
-        <v>6759891</v>
+        <v>6759931</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126826728</v>
+        <v>126825913</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436887</v>
+        <v>436759</v>
       </c>
       <c r="R5" t="n">
-        <v>6759925</v>
+        <v>6759891</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På flera tallstammar</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,50 +1113,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126826570</v>
+        <v>126826728</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436813</v>
+        <v>436887</v>
       </c>
       <c r="R6" t="n">
-        <v>6759931</v>
+        <v>6759925</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1193,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På flera tallstammar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1228,7 @@
         <v>126826931</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>126826915</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>126826644</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>91339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>126826327</v>
       </c>
       <c r="B10" t="n">
-        <v>75080</v>
+        <v>75073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>126826289</v>
       </c>
       <c r="B11" t="n">
-        <v>57821</v>
+        <v>57817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>126828249</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>98356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>126824791</v>
       </c>
       <c r="B13" t="n">
-        <v>75080</v>
+        <v>75073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>126825928</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>126825890</v>
       </c>
       <c r="B15" t="n">
-        <v>91350</v>
+        <v>91339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>126827015</v>
       </c>
       <c r="B16" t="n">
-        <v>91350</v>
+        <v>91339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>126826957</v>
       </c>
       <c r="B17" t="n">
-        <v>79042</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>126828191</v>
       </c>
       <c r="B18" t="n">
-        <v>4773</v>
+        <v>4772</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>126825242</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>126825163</v>
       </c>
       <c r="B20" t="n">
-        <v>75142</v>
+        <v>75135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>126827600</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>127284718</v>
       </c>
       <c r="B22" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>127284637</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>127284698</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126826809</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126826888</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126826570</v>
+        <v>126825913</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436813</v>
+        <v>436759</v>
       </c>
       <c r="R4" t="n">
-        <v>6759931</v>
+        <v>6759891</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126825913</v>
+        <v>126826728</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436759</v>
+        <v>436887</v>
       </c>
       <c r="R5" t="n">
-        <v>6759891</v>
+        <v>6759925</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>På flera tallstammar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,45 +1113,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126826728</v>
+        <v>126826570</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436887</v>
+        <v>436813</v>
       </c>
       <c r="R6" t="n">
-        <v>6759925</v>
+        <v>6759931</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1183,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,12 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera tallstammar</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1228,7 @@
         <v>126826931</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>126826915</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>126826644</v>
       </c>
       <c r="B9" t="n">
-        <v>91339</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>126826327</v>
       </c>
       <c r="B10" t="n">
-        <v>75073</v>
+        <v>75080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>126826289</v>
       </c>
       <c r="B11" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>126828249</v>
       </c>
       <c r="B12" t="n">
-        <v>98356</v>
+        <v>98368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>126824791</v>
       </c>
       <c r="B13" t="n">
-        <v>75073</v>
+        <v>75080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>126825928</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>126825890</v>
       </c>
       <c r="B15" t="n">
-        <v>91339</v>
+        <v>91350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>126827015</v>
       </c>
       <c r="B16" t="n">
-        <v>91339</v>
+        <v>91350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>126826957</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79042</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>126828191</v>
       </c>
       <c r="B18" t="n">
-        <v>4772</v>
+        <v>4773</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>126825242</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>126825163</v>
       </c>
       <c r="B20" t="n">
-        <v>75135</v>
+        <v>75142</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>126827600</v>
       </c>
       <c r="B21" t="n">
-        <v>98436</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>127284718</v>
       </c>
       <c r="B22" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>127284637</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>127284698</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126826809</v>
+        <v>126825890</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436957</v>
+        <v>436770</v>
       </c>
       <c r="R2" t="n">
-        <v>6759906</v>
+        <v>6759889</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126826888</v>
+        <v>126826644</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436997</v>
+        <v>436837</v>
       </c>
       <c r="R3" t="n">
-        <v>6759868</v>
+        <v>6759907</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126825913</v>
+        <v>126827015</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436759</v>
+        <v>436942</v>
       </c>
       <c r="R4" t="n">
-        <v>6759891</v>
+        <v>6760013</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126826728</v>
+        <v>126825913</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436887</v>
+        <v>436759</v>
       </c>
       <c r="R5" t="n">
-        <v>6759925</v>
+        <v>6759891</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1076,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På flera tallstammar</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,50 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126826570</v>
+        <v>126825928</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436813</v>
+        <v>436760</v>
       </c>
       <c r="R6" t="n">
-        <v>6759931</v>
+        <v>6759898</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1188,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,14 +1220,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126826931</v>
+        <v>126826728</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437020</v>
+        <v>436887</v>
       </c>
       <c r="R7" t="n">
-        <v>6759912</v>
+        <v>6759925</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1295,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1300,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På flera tallstammar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,14 +1332,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126826915</v>
+        <v>126826809</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437028</v>
+        <v>436957</v>
       </c>
       <c r="R8" t="n">
-        <v>6759907</v>
+        <v>6759906</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,32 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126826644</v>
+        <v>126826888</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436837</v>
+        <v>436997</v>
       </c>
       <c r="R9" t="n">
-        <v>6759907</v>
+        <v>6759868</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1546,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126826327</v>
+        <v>126826915</v>
       </c>
       <c r="B10" t="n">
-        <v>75080</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436654</v>
+        <v>437028</v>
       </c>
       <c r="R10" t="n">
-        <v>6759868</v>
+        <v>6759907</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,54 +1653,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126826289</v>
+        <v>126826931</v>
       </c>
       <c r="B11" t="n">
-        <v>57821</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436658</v>
+        <v>437020</v>
       </c>
       <c r="R11" t="n">
-        <v>6759873</v>
+        <v>6759912</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1732,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,41 +1760,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126828249</v>
+        <v>126824547</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>75428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223597</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Atugaturis, Atugaturis, Dlr</t>
+          <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436465</v>
+        <v>436547</v>
       </c>
       <c r="R12" t="n">
-        <v>6759903</v>
+        <v>6759690</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1835,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,11 +1870,11 @@
         <v>126824791</v>
       </c>
       <c r="B13" t="n">
-        <v>75080</v>
+        <v>75428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1979,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126825928</v>
+        <v>126826327</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>75428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436760</v>
+        <v>436654</v>
       </c>
       <c r="R14" t="n">
-        <v>6759898</v>
+        <v>6759868</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2049,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,12 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:32</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,32 +2081,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126825890</v>
+        <v>126826957</v>
       </c>
       <c r="B15" t="n">
-        <v>91350</v>
+        <v>79351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2126,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436770</v>
+        <v>437011</v>
       </c>
       <c r="R15" t="n">
-        <v>6759889</v>
+        <v>6759928</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2161,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2171,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126827015</v>
+        <v>126825163</v>
       </c>
       <c r="B16" t="n">
-        <v>91350</v>
+        <v>83307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2233,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436942</v>
+        <v>436643</v>
       </c>
       <c r="R16" t="n">
-        <v>6760013</v>
+        <v>6759772</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2268,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,45 +2295,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126826957</v>
+        <v>126825242</v>
       </c>
       <c r="B17" t="n">
-        <v>79042</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437011</v>
+        <v>436652</v>
       </c>
       <c r="R17" t="n">
-        <v>6759928</v>
+        <v>6759763</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2375,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2385,7 +2383,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosök ant.dubbelögad bastborren (Polygraphus poligraphus) som den har ätit mycket av.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,7 +2418,7 @@
         <v>126828191</v>
       </c>
       <c r="B18" t="n">
-        <v>4773</v>
+        <v>4775</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,10 +2527,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126825242</v>
+        <v>126826289</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,42 +2538,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436652</v>
+        <v>436658</v>
       </c>
       <c r="R19" t="n">
-        <v>6759763</v>
+        <v>6759873</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2602,7 +2606,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2612,12 +2616,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosök ant.dubbelögad bastborren (Polygraphus poligraphus) som den har ätit mycket av.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,45 +2643,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126825163</v>
+        <v>126826570</v>
       </c>
       <c r="B20" t="n">
-        <v>75142</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Råmossmyren, Råmossmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436643</v>
+        <v>436813</v>
       </c>
       <c r="R20" t="n">
-        <v>6759772</v>
+        <v>6759931</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2714,7 +2718,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2724,7 +2728,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2754,7 +2758,7 @@
         <v>126827600</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2867,10 +2871,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127284718</v>
+        <v>127284637</v>
       </c>
       <c r="B22" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2897,7 +2901,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2914,10 +2918,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436590</v>
+        <v>436603</v>
       </c>
       <c r="R22" t="n">
-        <v>6759954</v>
+        <v>6759843</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2949,7 +2953,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2959,7 +2963,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2987,10 +2991,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127284637</v>
+        <v>127284698</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3021,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3034,10 +3038,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436603</v>
+        <v>436602</v>
       </c>
       <c r="R23" t="n">
-        <v>6759843</v>
+        <v>6759946</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,7 +3073,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3079,7 +3083,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3107,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127284698</v>
+        <v>127284718</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3137,7 +3141,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3154,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436602</v>
+        <v>436590</v>
       </c>
       <c r="R24" t="n">
-        <v>6759946</v>
+        <v>6759954</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3224,6 +3228,109 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126828249</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Atugaturis, Atugaturis, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>436465</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6759903</v>
+      </c>
+      <c r="S25" t="n">
+        <v>9</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31562-2025 artfynd.xlsx
+++ b/artfynd/A 31562-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126825890</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826644</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126827015</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126825913</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126825928</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826728</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826809</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826888</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826915</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826931</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1864,6 +1919,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126824547</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1971,6 +2031,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126824791</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2078,6 +2143,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826327</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2185,6 +2255,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826957</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126825163</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2412,6 +2492,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126825242</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2524,6 +2609,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126828191</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2640,6 +2730,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826289</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2752,6 +2847,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826570</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2868,6 +2968,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126827600</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2988,6 +3093,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127284637</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3108,6 +3218,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127284698</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3228,6 +3343,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127284718</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3331,8 +3451,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126828249</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>